--- a/GF_X-master/AAAGameData/DataTables/LevelTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/LevelTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15270" windowHeight="17325"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>susum</author>
+  </authors>
+  <commentList>
+    <comment ref="J5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>susum:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.电话事件结束提前预告时间
+2.门事件结束提前预告时间
+3.窗事件结束提前预告时间</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
   <si>
     <t>#</t>
   </si>
@@ -59,12 +93,18 @@
     <t>LvTimer</t>
   </si>
   <si>
+    <t>globNum</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>float[]</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -86,6 +126,9 @@
     <t>关卡时间秒</t>
   </si>
   <si>
+    <t>固定值</t>
+  </si>
+  <si>
     <t>Lv_1-1</t>
   </si>
   <si>
@@ -93,6 +136,9 @@
   </si>
   <si>
     <t>Level.DisplayName1</t>
+  </si>
+  <si>
+    <t>1,2,2</t>
   </si>
   <si>
     <t>Level.DisplayName2</t>
@@ -117,7 +163,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,6 +324,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1052,18 +1109,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="15"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="7.87962962962963" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.37962962962963" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.12962962962963" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13.125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13.1296296296296" style="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="7.875" style="1"/>
+    <col min="10" max="10" width="7.87962962962963" style="1"/>
+    <col min="11" max="11" width="16.7777777777778" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="7.87962962962963" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -1077,14 +1136,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1103,72 +1161,80 @@
       <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>11</v>
+      </c>
       <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>10</v>
+      <c r="J3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:9">
+    <row r="4" s="1" customFormat="1" spans="1:10">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:9">
+    <row r="5" s="1" customFormat="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2">
         <v>200</v>
@@ -1177,10 +1243,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I5" s="1">
         <v>10</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:9">
@@ -1190,10 +1259,10 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" s="2">
         <v>160</v>
@@ -1202,7 +1271,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I6" s="1">
         <v>10</v>
@@ -1215,10 +1284,10 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2">
         <v>315</v>
@@ -1227,7 +1296,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1">
         <v>10</v>
@@ -1240,10 +1309,10 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F8" s="2">
         <v>210</v>
@@ -1252,7 +1321,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I8" s="1">
         <v>10</v>
@@ -1265,10 +1334,10 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9" s="2">
         <v>315</v>
@@ -1277,7 +1346,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1">
         <v>10</v>
@@ -1295,5 +1364,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/GF_X-master/AAAGameData/DataTables/LevelTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/LevelTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="17145" windowHeight="17325"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>#</t>
   </si>
@@ -144,13 +144,25 @@
     <t>Level.DisplayName2</t>
   </si>
   <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
     <t>Level.DisplayName3</t>
   </si>
   <si>
+    <t>1,2,4</t>
+  </si>
+  <si>
     <t>Level.DisplayName4</t>
   </si>
   <si>
+    <t>1,2,5</t>
+  </si>
+  <si>
     <t>Level.DisplayName5</t>
+  </si>
+  <si>
+    <t>1,2,6</t>
   </si>
 </sst>
 </file>
@@ -1110,19 +1122,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="7.87962962962963" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="7.88333333333333" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.37962962962963" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.12962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.38333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.8833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.13333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13.1296296296296" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13.1333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.87962962962963" style="1"/>
-    <col min="11" max="11" width="16.7777777777778" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="7.87962962962963" style="1"/>
+    <col min="10" max="10" width="7.88333333333333" style="1"/>
+    <col min="11" max="11" width="16.775" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="7.88333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -1252,7 +1264,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:9">
+    <row r="6" s="1" customFormat="1" spans="1:10">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
@@ -1276,8 +1288,11 @@
       <c r="I6" s="1">
         <v>10</v>
       </c>
+      <c r="J6" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:9">
+    <row r="7" s="1" customFormat="1" spans="1:10">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
@@ -1296,13 +1311,16 @@
         <v>6</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7" s="1">
         <v>10</v>
       </c>
+      <c r="J7" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:9">
+    <row r="8" s="1" customFormat="1" spans="1:10">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
@@ -1321,13 +1339,16 @@
         <v>6</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1">
         <v>10</v>
       </c>
+      <c r="J8" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:9">
+    <row r="9" s="1" customFormat="1" spans="1:10">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
@@ -1346,10 +1367,13 @@
         <v>3</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I9" s="1">
         <v>10</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/GF_X-master/AAAGameData/DataTables/LevelTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/LevelTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17145" windowHeight="17325"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
     <t>LvTimer</t>
   </si>
   <si>
-    <t>globNum</t>
+    <t>GlobNum</t>
   </si>
   <si>
     <t>int</t>
@@ -338,12 +338,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/GF_X-master/AAAGameData/DataTables/LevelTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/LevelTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -139,30 +139,6 @@
   </si>
   <si>
     <t>1,2,2</t>
-  </si>
-  <si>
-    <t>Level.DisplayName2</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
-    <t>Level.DisplayName3</t>
-  </si>
-  <si>
-    <t>1,2,4</t>
-  </si>
-  <si>
-    <t>Level.DisplayName4</t>
-  </si>
-  <si>
-    <t>1,2,5</t>
-  </si>
-  <si>
-    <t>Level.DisplayName5</t>
-  </si>
-  <si>
-    <t>1,2,6</t>
   </si>
 </sst>
 </file>
@@ -338,12 +314,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1264,117 +1240,45 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:10">
+    <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="2"/>
-      <c r="B6" s="2">
-        <v>2</v>
-      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="2">
-        <v>160</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="1">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:10">
+    <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="2"/>
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="2">
-        <v>315</v>
-      </c>
-      <c r="G7" s="2">
-        <v>6</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="1">
-        <v>10</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:10">
+    <row r="8" s="1" customFormat="1" spans="1:8">
       <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="2">
-        <v>210</v>
-      </c>
-      <c r="G8" s="2">
-        <v>6</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="1">
-        <v>10</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:10">
+    <row r="9" s="1" customFormat="1" spans="1:8">
       <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>5</v>
-      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="2">
-        <v>315</v>
-      </c>
-      <c r="G9" s="2">
-        <v>3</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="1">
-        <v>10</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="2">
